--- a/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
+++ b/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
@@ -8003,7 +8003,9 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0001</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8140,7 +8142,9 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0002</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8278,7 +8282,10 @@
       </c>
       <c r="N12" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0003</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O12" s="177" t="inlineStr">
@@ -8418,7 +8425,10 @@
       </c>
       <c r="N13" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0003</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O13" s="177" t="inlineStr">
@@ -8569,7 +8579,10 @@
       </c>
       <c r="N14" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0004</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O14" s="177" t="inlineStr">
@@ -8716,7 +8729,10 @@
       </c>
       <c r="N15" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0005</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O15" s="177" t="inlineStr">
@@ -8857,7 +8873,10 @@
       </c>
       <c r="N16" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0005</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O16" s="177" t="inlineStr">
@@ -9002,7 +9021,10 @@
       </c>
       <c r="N17" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0006</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O17" s="177" t="inlineStr">
@@ -9143,7 +9165,10 @@
       </c>
       <c r="N18" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0006</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O18" s="177" t="inlineStr">
@@ -9290,7 +9315,10 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0007</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9435,7 +9463,10 @@
       </c>
       <c r="N20" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0007</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O20" s="177" t="inlineStr">
@@ -9576,7 +9607,10 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0008</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9715,7 +9749,10 @@
       </c>
       <c r="N22" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0008</t>
+          <t xml:space="preserve">CFTS084-134366
+CFTS084-134369
+CFTS084-134370
+CFTS084-134371</t>
         </is>
       </c>
       <c r="O22" s="177" t="inlineStr">
@@ -9857,7 +9894,9 @@
       </c>
       <c r="N23" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0009</t>
+          <t xml:space="preserve">CFTS084-134372
+CFTS084-134373
+CFTS084-134374</t>
         </is>
       </c>
       <c r="O23" s="177" t="inlineStr">
@@ -9998,7 +10037,9 @@
       </c>
       <c r="N24" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0009</t>
+          <t xml:space="preserve">CFTS084-134372
+CFTS084-134373
+CFTS084-134374</t>
         </is>
       </c>
       <c r="O24" s="177" t="inlineStr">
@@ -10142,7 +10183,9 @@
       </c>
       <c r="N25" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0010</t>
+          <t xml:space="preserve">CFTS084-134372
+CFTS084-134373
+CFTS084-134374</t>
         </is>
       </c>
       <c r="O25" s="177" t="inlineStr">
@@ -10286,7 +10329,9 @@
       </c>
       <c r="N26" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0010</t>
+          <t xml:space="preserve">CFTS084-134372
+CFTS084-134373
+CFTS084-134374</t>
         </is>
       </c>
       <c r="O26" s="177" t="inlineStr">
@@ -10430,7 +10475,7 @@
       </c>
       <c r="N27" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0011</t>
+          <t xml:space="preserve">CFTS084-134368</t>
         </is>
       </c>
       <c r="O27" s="177" t="inlineStr">
@@ -10574,7 +10619,7 @@
       </c>
       <c r="N28" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
+          <t xml:space="preserve">CFTS084-134386</t>
         </is>
       </c>
       <c r="O28" s="177" t="inlineStr">
@@ -10718,7 +10763,7 @@
       </c>
       <c r="N29" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
+          <t xml:space="preserve">CFTS084-134386</t>
         </is>
       </c>
       <c r="O29" s="177" t="inlineStr">
@@ -10859,7 +10904,7 @@
       </c>
       <c r="N30" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0012</t>
+          <t xml:space="preserve">CFTS084-134386</t>
         </is>
       </c>
       <c r="O30" s="177" t="inlineStr">
@@ -10999,7 +11044,7 @@
       </c>
       <c r="N31" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O31" s="81" t="inlineStr">
@@ -11139,7 +11184,7 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11279,7 +11324,7 @@
       </c>
       <c r="N33" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O33" s="177" t="inlineStr">
@@ -11420,7 +11465,7 @@
       </c>
       <c r="N34" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0013</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O34" s="177" t="inlineStr">
@@ -11561,7 +11606,7 @@
       </c>
       <c r="N35" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0014</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O35" s="177" t="inlineStr">
@@ -11711,7 +11756,7 @@
       </c>
       <c r="N36" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0015</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O36" s="177" t="inlineStr">
@@ -11852,7 +11897,7 @@
       </c>
       <c r="N37" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0016</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O37" s="177" t="inlineStr">
@@ -11993,7 +12038,7 @@
       </c>
       <c r="N38" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0016</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O38" s="177" t="inlineStr">
@@ -12133,7 +12178,7 @@
       </c>
       <c r="N39" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0017</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O39" s="81" t="inlineStr">
@@ -12272,7 +12317,7 @@
       </c>
       <c r="N40" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0017</t>
+          <t xml:space="preserve">CFTS084-134385</t>
         </is>
       </c>
       <c r="O40" s="81" t="inlineStr">
@@ -12411,7 +12456,9 @@
       </c>
       <c r="N41" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0018</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O41" s="81" t="inlineStr">
@@ -12546,7 +12593,9 @@
       </c>
       <c r="N42" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1-SAM-SWE1R1-V1.1_SWE1-SAM-0019</t>
+          <t xml:space="preserve">CFTS084-134367
+CFTS084-134383
+CFTS084-134384</t>
         </is>
       </c>
       <c r="O42" s="81" t="inlineStr">

--- a/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
+++ b/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SAM_20260917.xlsx
@@ -8003,9 +8003,9 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8142,9 +8142,9 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8282,10 +8282,10 @@
       </c>
       <c r="N12" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O12" s="177" t="inlineStr">
@@ -8425,10 +8425,10 @@
       </c>
       <c r="N13" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O13" s="177" t="inlineStr">
@@ -8579,10 +8579,10 @@
       </c>
       <c r="N14" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O14" s="177" t="inlineStr">
@@ -8729,10 +8729,10 @@
       </c>
       <c r="N15" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O15" s="177" t="inlineStr">
@@ -8873,10 +8873,10 @@
       </c>
       <c r="N16" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O16" s="177" t="inlineStr">
@@ -9021,10 +9021,10 @@
       </c>
       <c r="N17" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O17" s="177" t="inlineStr">
@@ -9165,10 +9165,10 @@
       </c>
       <c r="N18" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O18" s="177" t="inlineStr">
@@ -9315,10 +9315,10 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9463,10 +9463,10 @@
       </c>
       <c r="N20" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O20" s="177" t="inlineStr">
@@ -9607,10 +9607,10 @@
       </c>
       <c r="N21" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O21" s="81" t="inlineStr">
@@ -9749,10 +9749,10 @@
       </c>
       <c r="N22" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134366
-CFTS084-134369
-CFTS084-134370
-CFTS084-134371</t>
+          <t xml:space="preserve">CFTS084-4949331
+CFTS084-4949334
+CFTS084-4949336
+CFTS084-4949337</t>
         </is>
       </c>
       <c r="O22" s="177" t="inlineStr">
@@ -9894,9 +9894,9 @@
       </c>
       <c r="N23" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134372
-CFTS084-134373
-CFTS084-134374</t>
+          <t xml:space="preserve">CFTS084-4949338
+CFTS084-4949339
+CFTS084-4949340</t>
         </is>
       </c>
       <c r="O23" s="177" t="inlineStr">
@@ -10037,9 +10037,9 @@
       </c>
       <c r="N24" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134372
-CFTS084-134373
-CFTS084-134374</t>
+          <t xml:space="preserve">CFTS084-4949338
+CFTS084-4949339
+CFTS084-4949340</t>
         </is>
       </c>
       <c r="O24" s="177" t="inlineStr">
@@ -10183,9 +10183,9 @@
       </c>
       <c r="N25" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134372
-CFTS084-134373
-CFTS084-134374</t>
+          <t xml:space="preserve">CFTS084-4949338
+CFTS084-4949339
+CFTS084-4949340</t>
         </is>
       </c>
       <c r="O25" s="177" t="inlineStr">
@@ -10329,9 +10329,9 @@
       </c>
       <c r="N26" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134372
-CFTS084-134373
-CFTS084-134374</t>
+          <t xml:space="preserve">CFTS084-4949338
+CFTS084-4949339
+CFTS084-4949340</t>
         </is>
       </c>
       <c r="O26" s="177" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="N27" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134368</t>
+          <t xml:space="preserve">CFTS084-4949333</t>
         </is>
       </c>
       <c r="O27" s="177" t="inlineStr">
@@ -10619,7 +10619,7 @@
       </c>
       <c r="N28" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134386</t>
+          <t xml:space="preserve">CFTS084-4949354</t>
         </is>
       </c>
       <c r="O28" s="177" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="N29" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134386</t>
+          <t xml:space="preserve">CFTS084-4949354</t>
         </is>
       </c>
       <c r="O29" s="177" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="N30" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134386</t>
+          <t xml:space="preserve">CFTS084-4949354</t>
         </is>
       </c>
       <c r="O30" s="177" t="inlineStr">
@@ -11044,7 +11044,7 @@
       </c>
       <c r="N31" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O31" s="81" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="N32" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O32" s="81" t="inlineStr">
@@ -11324,7 +11324,7 @@
       </c>
       <c r="N33" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O33" s="177" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="N34" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O34" s="177" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="N35" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O35" s="177" t="inlineStr">
@@ -11756,7 +11756,7 @@
       </c>
       <c r="N36" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O36" s="177" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="N37" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O37" s="177" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="N38" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O38" s="177" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="N39" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O39" s="81" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="N40" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134385</t>
+          <t xml:space="preserve">CFTS084-4949353</t>
         </is>
       </c>
       <c r="O40" s="81" t="inlineStr">
@@ -12456,9 +12456,9 @@
       </c>
       <c r="N41" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O41" s="81" t="inlineStr">
@@ -12593,9 +12593,9 @@
       </c>
       <c r="N42" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134367
-CFTS084-134383
-CFTS084-134384</t>
+          <t xml:space="preserve">CFTS084-4949332
+CFTS084-4949351
+CFTS084-4949352</t>
         </is>
       </c>
       <c r="O42" s="81" t="inlineStr">
